--- a/stencil/3.3、招标文件-导入清单（电子版、与招标文件采购清单一致）.xlsx
+++ b/stencil/3.3、招标文件-导入清单（电子版、与招标文件采购清单一致）.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14175"/>
+    <workbookView windowWidth="26295" windowHeight="4170"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1554,7 +1554,9 @@
     <col min="14" max="15" width="9.375" style="1"/>
     <col min="16" max="16" width="14.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="9.75" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="18" max="19" width="9" style="1"/>
+    <col min="20" max="20" width="12.625" style="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
